--- a/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/Manual testing results.xlsx
+++ b/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/Manual testing results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AminD\OneDrive\Desktop\Work\Fraunhofer Job\Work\Code\Paper repository scraping Code\requirement_checks\5.1.code_availability\5.1.3.pre-processing_&amp;_pipeline_code\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290BC504-26FF-4DC5-9A51-980B2E5478B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0707D447-1B56-4403-A011-C053F0BC44ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -208,6 +208,70 @@
   </si>
   <si>
     <t xml:space="preserve">scripts/utils.py, </t>
+  </si>
+  <si>
+    <t>_preprocess.py</t>
+  </si>
+  <si>
+    <t>def preprocess_reservoir_data(data_path="./graph/data", output_path="./graph/data/parsed", _input_features=3, _days_x=30, _days_y=7, scaler_type="global"):
+    """Preprocess all reservoir data with time-based splitting and sliding windows
+    Args:
+        data_path (str): Path to the input data directory
+        output_path (str): Path to save processed data
+        _input_features (int): Number of input features
+        _days_x (int): Number of input days
+        _days_y (int): Number of prediction days
+        scaler_type (str): Type of scaler to use. Options: 'global' or 'local'
+    Returns:
+        dict: Dictionary containing processed data for all reservoirs
+    """</t>
+  </si>
+  <si>
+    <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+  </si>
+  <si>
+    <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+  </si>
+  <si>
+    <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+  </si>
+  <si>
+    <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+  </si>
+  <si>
+    <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+  </si>
+  <si>
+    <t>https://github.com/ZJUFanLab/MSformer</t>
+  </si>
+  <si>
+    <t>Advancing site-specific disease and pest management in precision agriculture: From reasoning-driven foundation models to adaptive, feedback-based learning</t>
+  </si>
+  <si>
+    <t>https://github.com/nitin-dominic/AgriPathogenDatabase</t>
+  </si>
+  <si>
+    <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+  </si>
+  <si>
+    <t>https://github.com/zacharyyahn/AFOG</t>
+  </si>
+  <si>
+    <t>class MSEncoder:
+    """Molecular Substructure Encoder for chemical fragment representation learning
+    Attributes:
+        model (LightningModule): Pretrained transformer model
+        tokenizer (MolTranBertTokenizer): Chemical tokenizer
+        device (torch.device): Computation device (GPU/CPU)
+        max_fragments (int): Maximum number of fragments per molecule
+        embed_dim (int): Dimension of fragment embeddings
+    Methods:
+        encode(fragments: List[List[str]]) -&gt; np.ndarray
+        save_embeddings(embeddings: np.ndarray, output_path: str)
+    """</t>
+  </si>
+  <si>
+    <t>msformer/MSEncoder.py</t>
   </si>
 </sst>
 </file>
@@ -338,7 +402,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -370,6 +434,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -390,6 +457,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -674,19 +753,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="98.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="50" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" style="16" customWidth="1"/>
     <col min="6" max="6" width="55" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.140625" style="11" customWidth="1"/>
     <col min="8" max="8" width="62.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -696,10 +775,10 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -712,7 +791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -722,21 +801,21 @@
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>29</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="19" t="s">
         <v>31</v>
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="120.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="120.75" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -746,21 +825,21 @@
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="20" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -770,21 +849,21 @@
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="20" t="s">
         <v>37</v>
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -794,21 +873,21 @@
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="20" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -816,15 +895,15 @@
       <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -834,91 +913,204 @@
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="20" t="s">
         <v>40</v>
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="19"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="19"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" ht="153" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="153" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="F10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="20" t="s">
         <v>44</v>
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7"/>
+      <c r="B11" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="C11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="21">
+        <v>15</v>
+      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/Manual testing results.xlsx
+++ b/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/Manual testing results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AminD\OneDrive\Desktop\Work\Fraunhofer Job\Work\Code\Paper repository scraping Code\requirement_checks\5.1.code_availability\5.1.3.pre-processing_&amp;_pipeline_code\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0707D447-1B56-4403-A011-C053F0BC44ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63364CE3-AA58-4CD4-8478-F9BB2E88D06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -233,6 +233,9 @@
     <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
   </si>
   <si>
+    <t>Hannah+Walker_Paper.ipynb</t>
+  </si>
+  <si>
     <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
   </si>
   <si>
@@ -272,6 +275,26 @@
   </si>
   <si>
     <t>msformer/MSEncoder.py</t>
+  </si>
+  <si>
+    <t>utils/dataset_utils/voc/preprocessing.py</t>
+  </si>
+  <si>
+    <t>def letterbox_image_padded(image, size=(416, 416)):
+    """ Resize image with unchanged aspect ratio using padding """
+    image_copy = image.copy()
+    iw, ih = image_copy.size
+    w, h = size
+    scale = min(w / iw, h / ih)
+    nw = int(iw * scale)
+    nh = int(ih * scale)</t>
+  </si>
+  <si>
+    <t>Not sure</t>
+  </si>
+  <si>
+    <t>if PQ:
+        query = f"Is it true that '{P}' implies '{Q}'? Answer with 'yes' or 'no'."</t>
   </si>
 </sst>
 </file>
@@ -422,9 +445,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -433,6 +453,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -795,7 +818,7 @@
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -819,7 +842,7 @@
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -831,7 +854,7 @@
       <c r="E3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -843,7 +866,7 @@
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -855,7 +878,7 @@
       <c r="E4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -867,7 +890,7 @@
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -879,7 +902,7 @@
       <c r="E5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -891,7 +914,9 @@
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
@@ -901,13 +926,15 @@
       <c r="E6" s="15"/>
       <c r="F6" s="2"/>
       <c r="G6" s="19"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="10" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -919,7 +946,7 @@
       <c r="E7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="20" t="s">
@@ -967,7 +994,7 @@
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -979,7 +1006,7 @@
       <c r="E10" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="20" t="s">
@@ -991,7 +1018,7 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1001,7 +1028,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="15"/>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>46</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -1013,8 +1040,8 @@
       <c r="A12" s="21">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>42</v>
+      <c r="B12" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>47</v>
@@ -1022,95 +1049,110 @@
       <c r="D12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
+      <c r="E12" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>12</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>13</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="C14" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="21">
         <v>14</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="C15" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="10"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="20"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>15</v>
       </c>
-      <c r="B16" s="22"/>
+      <c r="B16" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="C16" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="20"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="F16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
